--- a/outputs/landed_cost_2026-09.xlsx
+++ b/outputs/landed_cost_2026-09.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -579,60 +579,100 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>МАШИНА: с наценкой, KRW</t>
+          <t>МАШИНА: товар без расходов, руб</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>187118100</v>
+        <v>8348346</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>МАШИНА: с наценкой, руб</t>
+          <t>МАШИНА: расходы до Москвы, руб</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10852850</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ВСЕГО в пути, руб</t>
+          <t>МАШИНА: это процент к цене товара</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>54606631</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Недогружено против заказа, шт</t>
+          <t>МАШИНА: расходы на штуку, руб</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>600</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Инвойс выставлен на недогруз, KRW</t>
+          <t>МАШИНА: с расходами, KRW</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>161178379</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>МАШИНА: с расходами, руб</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>9348346</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ВСЕГО в пути, руб</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>53102128</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Недогружено против заказа, шт</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Инвойс выставлен на недогруз, KRW</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Позиций без цены</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2817,20 +2857,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2851,40 +2894,55 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Вес брутто, кг</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Срок годности</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Источник цены</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Цена, KRW</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Цена до Москвы, KRW</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Себестоимость, руб/шт</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Сумма, KRW</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Расходы по стоимости, руб</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Расходы по весу, руб</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Сумма до Москвы, KRW</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Сумма, руб</t>
         </is>
@@ -2904,33 +2962,42 @@
       <c r="C2" s="2" t="n">
         <v>15000</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>3812.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>2028-09-23</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>инвойс контейнера</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>8930</v>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>11609</v>
-      </c>
       <c r="H2" s="2" t="n">
-        <v>673.3200000000001</v>
+        <v>10000</v>
       </c>
       <c r="I2" s="2" t="n">
+        <v>579.98</v>
+      </c>
+      <c r="J2" s="2" t="n">
         <v>133950000</v>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>174135000</v>
-      </c>
       <c r="K2" s="2" t="n">
-        <v>10099830</v>
+        <v>930615</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>903972</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>149995094</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>8699715</v>
       </c>
     </row>
     <row r="3">
@@ -2947,33 +3014,42 @@
       <c r="C3" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>2029-04-27</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>прайс Классик</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="G3" s="2" t="n">
         <v>4000</v>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>5200</v>
-      </c>
       <c r="H3" s="2" t="n">
-        <v>301.6</v>
+        <v>4479</v>
       </c>
       <c r="I3" s="2" t="n">
+        <v>259.79</v>
+      </c>
+      <c r="J3" s="2" t="n">
         <v>4000000</v>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>5200000</v>
-      </c>
       <c r="K3" s="2" t="n">
-        <v>301600</v>
+        <v>27790</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>35566</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>4479137</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>259790</v>
       </c>
     </row>
     <row r="4">
@@ -2990,33 +3066,42 @@
       <c r="C4" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>2029-01-08</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>прайс Классик</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>4130</v>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>5369</v>
-      </c>
       <c r="H4" s="2" t="n">
-        <v>311.4</v>
+        <v>4625</v>
       </c>
       <c r="I4" s="2" t="n">
+        <v>268.23</v>
+      </c>
+      <c r="J4" s="2" t="n">
         <v>826000</v>
       </c>
-      <c r="J4" s="2" t="n">
-        <v>1073800</v>
-      </c>
       <c r="K4" s="2" t="n">
-        <v>62280</v>
+        <v>5739</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>7113</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>924942</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>53647</v>
       </c>
     </row>
     <row r="5">
@@ -3033,33 +3118,42 @@
       <c r="C5" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="n">
+        <v>60</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>2029-05-10</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>прайс Классик</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="G5" s="2" t="n">
         <v>4130</v>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>5369</v>
-      </c>
       <c r="H5" s="2" t="n">
-        <v>311.4</v>
+        <v>4625</v>
       </c>
       <c r="I5" s="2" t="n">
+        <v>268.23</v>
+      </c>
+      <c r="J5" s="2" t="n">
         <v>1652000</v>
       </c>
-      <c r="J5" s="2" t="n">
-        <v>2147600</v>
-      </c>
       <c r="K5" s="2" t="n">
-        <v>124561</v>
+        <v>11477</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>14226</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>1849884</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>107293</v>
       </c>
     </row>
     <row r="6">
@@ -3076,33 +3170,42 @@
       <c r="C6" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="n">
+        <v>105</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>2029-04-13</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>прайс Классик</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>3190</v>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>4147</v>
-      </c>
       <c r="H6" s="2" t="n">
-        <v>240.53</v>
+        <v>3572</v>
       </c>
       <c r="I6" s="2" t="n">
+        <v>207.18</v>
+      </c>
+      <c r="J6" s="2" t="n">
         <v>2233000</v>
       </c>
-      <c r="J6" s="2" t="n">
-        <v>2902900</v>
-      </c>
       <c r="K6" s="2" t="n">
-        <v>168368</v>
+        <v>15514</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>24896</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>2500478</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>145028</v>
       </c>
     </row>
     <row r="7">
@@ -3119,33 +3222,42 @@
       <c r="C7" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="n">
+        <v>60</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>2028-09-18</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>прайс Классик</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="G7" s="2" t="n">
         <v>3190</v>
       </c>
-      <c r="G7" s="2" t="n">
-        <v>4147</v>
-      </c>
       <c r="H7" s="2" t="n">
-        <v>240.53</v>
+        <v>3572</v>
       </c>
       <c r="I7" s="2" t="n">
+        <v>207.18</v>
+      </c>
+      <c r="J7" s="2" t="n">
         <v>1276000</v>
       </c>
-      <c r="J7" s="2" t="n">
-        <v>1658800</v>
-      </c>
       <c r="K7" s="2" t="n">
-        <v>96210</v>
+        <v>8865</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>14226</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>1428845</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>82873</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/landed_cost_2026-09.xlsx
+++ b/outputs/landed_cost_2026-09.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>143937000</v>
+        <v>164487000</v>
       </c>
     </row>
     <row r="14">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8348346</v>
+        <v>9540246</v>
       </c>
     </row>
     <row r="15">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="17">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>161178379</v>
+        <v>181728379</v>
       </c>
     </row>
     <row r="19">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9348346</v>
+        <v>10540246</v>
       </c>
     </row>
     <row r="20">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>53102128</v>
+        <v>54294028</v>
       </c>
     </row>
     <row r="21">
@@ -2972,32 +2972,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>инвойс контейнера</t>
+          <t>названа по этой поставке</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>8930</v>
+        <v>10300</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10000</v>
+        <v>11380</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>579.98</v>
+        <v>660.02</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>133950000</v>
+        <v>154500000</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>930615</v>
+        <v>939284</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>903972</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>149995094</v>
+        <v>170694551</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>8699715</v>
+        <v>9900284</v>
       </c>
     </row>
     <row r="3">
@@ -3031,25 +3031,25 @@
         <v>4000</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>4479</v>
+        <v>4419</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>259.79</v>
+        <v>256.32</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>4000000</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>27790</v>
+        <v>24318</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>35566</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4479137</v>
+        <v>4419276</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>259790</v>
+        <v>256318</v>
       </c>
     </row>
     <row r="4">
@@ -3083,25 +3083,25 @@
         <v>4130</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>4625</v>
+        <v>4563</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>268.23</v>
+        <v>264.65</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>826000</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>5739</v>
+        <v>5022</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>7113</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>924942</v>
+        <v>912581</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>53647</v>
+        <v>52930</v>
       </c>
     </row>
     <row r="5">
@@ -3135,25 +3135,25 @@
         <v>4130</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>4625</v>
+        <v>4563</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>268.23</v>
+        <v>264.65</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1652000</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>11477</v>
+        <v>10043</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>14226</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1849884</v>
+        <v>1825161</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>107293</v>
+        <v>105859</v>
       </c>
     </row>
     <row r="6">
@@ -3187,25 +3187,25 @@
         <v>3190</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>3572</v>
+        <v>3524</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>207.18</v>
+        <v>204.41</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>2233000</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>15514</v>
+        <v>13576</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>24896</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2500478</v>
+        <v>2467061</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>145028</v>
+        <v>143090</v>
       </c>
     </row>
     <row r="7">
@@ -3239,25 +3239,25 @@
         <v>3190</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>3572</v>
+        <v>3524</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>207.18</v>
+        <v>204.41</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1276000</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>8865</v>
+        <v>7757</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>14226</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1428845</v>
+        <v>1409749</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>82873</v>
+        <v>81765</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/landed_cost_2026-09.xlsx
+++ b/outputs/landed_cost_2026-09.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.058</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="4">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43753782</v>
+        <v>46771284</v>
       </c>
     </row>
     <row r="11">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9540246</v>
+        <v>10198194</v>
       </c>
     </row>
     <row r="15">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>181728379</v>
+        <v>180616032</v>
       </c>
     </row>
     <row r="19">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10540246</v>
+        <v>11198194</v>
       </c>
     </row>
     <row r="20">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>54294028</v>
+        <v>57969478</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         <v>11609</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>673.3200000000001</v>
+        <v>719.76</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>223321440</v>
@@ -813,7 +813,7 @@
         <v>290317872</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>16838437</v>
+        <v>17999708</v>
       </c>
       <c r="M2" t="inlineStr"/>
     </row>
@@ -846,7 +846,7 @@
         <v>9555</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>554.1900000000001</v>
+        <v>592.41</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>8820000</v>
@@ -858,7 +858,7 @@
         <v>11466000</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>665028</v>
+        <v>710892</v>
       </c>
       <c r="M3" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         <v>9880</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>573.04</v>
+        <v>612.5599999999999</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>3648000</v>
@@ -903,7 +903,7 @@
         <v>4742400</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>275059</v>
+        <v>294029</v>
       </c>
       <c r="M4" t="inlineStr"/>
     </row>
@@ -936,7 +936,7 @@
         <v>7020</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>407.16</v>
+        <v>435.24</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>2419200</v>
@@ -948,7 +948,7 @@
         <v>3144960</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>182408</v>
+        <v>194988</v>
       </c>
       <c r="M5" t="inlineStr"/>
     </row>
@@ -981,7 +981,7 @@
         <v>8515</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>493.87</v>
+        <v>527.9299999999999</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>2043600</v>
@@ -993,7 +993,7 @@
         <v>2656680</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>154087</v>
+        <v>164714</v>
       </c>
       <c r="M6" t="inlineStr"/>
     </row>
@@ -1026,7 +1026,7 @@
         <v>9230</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>535.34</v>
+        <v>572.26</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>2236500</v>
@@ -1038,7 +1038,7 @@
         <v>2907450</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>168632</v>
+        <v>180262</v>
       </c>
       <c r="M7" t="inlineStr"/>
     </row>
@@ -1071,7 +1071,7 @@
         <v>11115</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>644.67</v>
+        <v>689.13</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>8413200</v>
@@ -1083,7 +1083,7 @@
         <v>10937160</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>634355</v>
+        <v>678104</v>
       </c>
       <c r="M8" t="inlineStr"/>
     </row>
@@ -1116,7 +1116,7 @@
         <v>10504</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>609.23</v>
+        <v>651.25</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>9696000</v>
@@ -1128,7 +1128,7 @@
         <v>12604800</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>731078</v>
+        <v>781498</v>
       </c>
       <c r="M9" t="inlineStr"/>
     </row>
@@ -1161,7 +1161,7 @@
         <v>12909</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>748.72</v>
+        <v>800.36</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>8579520</v>
@@ -1173,7 +1173,7 @@
         <v>11153376</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>646896</v>
+        <v>691509</v>
       </c>
       <c r="M10" t="inlineStr"/>
     </row>
@@ -1206,7 +1206,7 @@
         <v>15002</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>870.12</v>
+        <v>930.12</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>8308800</v>
@@ -1218,7 +1218,7 @@
         <v>10801440</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>626484</v>
+        <v>669689</v>
       </c>
       <c r="M11" t="inlineStr"/>
     </row>
@@ -1251,7 +1251,7 @@
         <v>12311</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>714.04</v>
+        <v>763.28</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>5682000</v>
@@ -1263,7 +1263,7 @@
         <v>7386600</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>428423</v>
+        <v>457969</v>
       </c>
       <c r="M12" t="inlineStr"/>
     </row>
@@ -1296,7 +1296,7 @@
         <v>8281</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>480.3</v>
+        <v>513.42</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>3669120</v>
@@ -1308,7 +1308,7 @@
         <v>4769856</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>276652</v>
+        <v>295731</v>
       </c>
       <c r="M13" t="inlineStr"/>
     </row>
@@ -1341,7 +1341,7 @@
         <v>7917</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>459.19</v>
+        <v>490.85</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>3215520</v>
@@ -1353,7 +1353,7 @@
         <v>4180176</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>242450</v>
+        <v>259171</v>
       </c>
       <c r="M14" t="inlineStr"/>
     </row>
@@ -1386,7 +1386,7 @@
         <v>8918</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>517.24</v>
+        <v>552.92</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>2414720</v>
@@ -1398,7 +1398,7 @@
         <v>3139136</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>182070</v>
+        <v>194626</v>
       </c>
       <c r="M15" t="inlineStr"/>
     </row>
@@ -1431,7 +1431,7 @@
         <v>10426</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>604.71</v>
+        <v>646.41</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>2309760</v>
@@ -1443,7 +1443,7 @@
         <v>3002688</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>174156</v>
+        <v>186167</v>
       </c>
       <c r="M16" t="inlineStr"/>
     </row>
@@ -1476,7 +1476,7 @@
         <v>8593</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>498.39</v>
+        <v>532.77</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>2696880</v>
@@ -1488,7 +1488,7 @@
         <v>3505944</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>203345</v>
+        <v>217369</v>
       </c>
       <c r="M17" t="inlineStr"/>
     </row>
@@ -1521,7 +1521,7 @@
         <v>8307</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>481.81</v>
+        <v>515.03</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>2990520</v>
@@ -1533,7 +1533,7 @@
         <v>3887676</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>225485</v>
+        <v>241036</v>
       </c>
       <c r="M18" t="inlineStr"/>
     </row>
@@ -1566,7 +1566,7 @@
         <v>6682</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>387.56</v>
+        <v>414.28</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>1644800</v>
@@ -1578,7 +1578,7 @@
         <v>2138240</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>124018</v>
+        <v>132571</v>
       </c>
       <c r="M19" t="inlineStr"/>
     </row>
@@ -1611,7 +1611,7 @@
         <v>8086</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>468.99</v>
+        <v>501.33</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>155624400</v>
@@ -1623,7 +1623,7 @@
         <v>202311720</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>11734080</v>
+        <v>12543327</v>
       </c>
       <c r="M20" t="inlineStr"/>
     </row>
@@ -1656,7 +1656,7 @@
         <v>9295</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>539.11</v>
+        <v>576.29</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>4290000</v>
@@ -1668,7 +1668,7 @@
         <v>5577000</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>323466</v>
+        <v>345774</v>
       </c>
       <c r="M21" t="inlineStr"/>
     </row>
@@ -1701,7 +1701,7 @@
         <v>8294</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>481.05</v>
+        <v>514.23</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>3828000</v>
@@ -1713,7 +1713,7 @@
         <v>4976400</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>288631</v>
+        <v>308537</v>
       </c>
       <c r="M22" t="inlineStr"/>
     </row>
@@ -1746,7 +1746,7 @@
         <v>9867</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>572.29</v>
+        <v>611.75</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>3036000</v>
@@ -1758,7 +1758,7 @@
         <v>3946800</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>228914</v>
+        <v>244702</v>
       </c>
       <c r="M23" t="inlineStr"/>
     </row>
@@ -1791,7 +1791,7 @@
         <v>14560</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>844.48</v>
+        <v>902.72</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>2688000</v>
@@ -1803,7 +1803,7 @@
         <v>3494400</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>202675</v>
+        <v>216653</v>
       </c>
       <c r="M24" t="inlineStr"/>
     </row>
@@ -1836,7 +1836,7 @@
         <v>15561</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>902.54</v>
+        <v>964.78</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>4788000</v>
@@ -1848,7 +1848,7 @@
         <v>6224400</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>361015</v>
+        <v>385913</v>
       </c>
       <c r="M25" t="inlineStr"/>
     </row>
@@ -1881,7 +1881,7 @@
         <v>9848</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>571.16</v>
+        <v>610.54</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>2727000</v>
@@ -1893,7 +1893,7 @@
         <v>3545100</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>205616</v>
+        <v>219796</v>
       </c>
       <c r="M26" t="inlineStr"/>
     </row>
@@ -1926,7 +1926,7 @@
         <v>13000</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>754</v>
+        <v>806</v>
       </c>
       <c r="I27" s="2" t="n">
         <v>2700000</v>
@@ -1938,7 +1938,7 @@
         <v>3510000</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>203580</v>
+        <v>217620</v>
       </c>
       <c r="M27" t="inlineStr"/>
     </row>
@@ -1971,7 +1971,7 @@
         <v>13650</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>791.7</v>
+        <v>846.3</v>
       </c>
       <c r="I28" s="2" t="n">
         <v>2205000</v>
@@ -1983,7 +1983,7 @@
         <v>2866500</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>166257</v>
+        <v>177723</v>
       </c>
       <c r="M28" t="inlineStr"/>
     </row>
@@ -2016,7 +2016,7 @@
         <v>7735</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>448.63</v>
+        <v>479.57</v>
       </c>
       <c r="I29" s="2" t="n">
         <v>1785000</v>
@@ -2028,7 +2028,7 @@
         <v>2320500</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>134589</v>
+        <v>143871</v>
       </c>
       <c r="M29" t="inlineStr"/>
     </row>
@@ -2061,7 +2061,7 @@
         <v>10530</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>610.74</v>
+        <v>652.86</v>
       </c>
       <c r="I30" s="2" t="n">
         <v>12150000</v>
@@ -2073,7 +2073,7 @@
         <v>15795000</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>916110</v>
+        <v>979290</v>
       </c>
       <c r="M30" t="inlineStr"/>
     </row>
@@ -2106,7 +2106,7 @@
         <v>13520</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>784.16</v>
+        <v>838.24</v>
       </c>
       <c r="I31" s="2" t="n">
         <v>9360000</v>
@@ -2118,7 +2118,7 @@
         <v>12168000</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>705744</v>
+        <v>754416</v>
       </c>
       <c r="M31" t="inlineStr"/>
     </row>
@@ -2151,7 +2151,7 @@
         <v>13390</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>776.62</v>
+        <v>830.1799999999999</v>
       </c>
       <c r="I32" s="2" t="n">
         <v>9476000</v>
@@ -2163,7 +2163,7 @@
         <v>12318800</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>714490</v>
+        <v>763766</v>
       </c>
       <c r="M32" t="inlineStr"/>
     </row>
@@ -2196,7 +2196,7 @@
         <v>13780</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>799.24</v>
+        <v>854.36</v>
       </c>
       <c r="I33" s="2" t="n">
         <v>3392000</v>
@@ -2208,7 +2208,7 @@
         <v>4409600</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>255757</v>
+        <v>273395</v>
       </c>
       <c r="M33" t="inlineStr"/>
     </row>
@@ -2241,7 +2241,7 @@
         <v>17030</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>987.74</v>
+        <v>1055.86</v>
       </c>
       <c r="I34" s="2" t="n">
         <v>5240000</v>
@@ -2253,7 +2253,7 @@
         <v>6812000</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>395096</v>
+        <v>422344</v>
       </c>
       <c r="M34" t="inlineStr"/>
     </row>
@@ -2286,7 +2286,7 @@
         <v>15470</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>897.26</v>
+        <v>959.14</v>
       </c>
       <c r="I35" s="2" t="n">
         <v>3570000</v>
@@ -2298,7 +2298,7 @@
         <v>4641000</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>269178</v>
+        <v>287742</v>
       </c>
       <c r="M35" t="inlineStr"/>
     </row>
@@ -2331,7 +2331,7 @@
         <v>18837</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>1092.55</v>
+        <v>1167.89</v>
       </c>
       <c r="I36" s="2" t="n">
         <v>3477600</v>
@@ -2343,7 +2343,7 @@
         <v>4520880</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>262211</v>
+        <v>280295</v>
       </c>
       <c r="M36" t="inlineStr"/>
     </row>
@@ -2376,7 +2376,7 @@
         <v>20826</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>1207.91</v>
+        <v>1291.21</v>
       </c>
       <c r="I37" s="2" t="n">
         <v>2563200</v>
@@ -2388,7 +2388,7 @@
         <v>3332160</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>193265</v>
+        <v>206594</v>
       </c>
       <c r="M37" t="inlineStr"/>
     </row>
@@ -2421,7 +2421,7 @@
         <v>13692</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>794.11</v>
+        <v>848.88</v>
       </c>
       <c r="I38" s="2" t="n">
         <v>2106400</v>
@@ -2433,7 +2433,7 @@
         <v>2738320</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>158823</v>
+        <v>169776</v>
       </c>
       <c r="M38" t="inlineStr"/>
     </row>
@@ -2466,7 +2466,7 @@
         <v>10790</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>625.8200000000001</v>
+        <v>668.98</v>
       </c>
       <c r="I39" s="2" t="n">
         <v>4382400</v>
@@ -2478,7 +2478,7 @@
         <v>5697120</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>330433</v>
+        <v>353221</v>
       </c>
       <c r="M39" t="inlineStr"/>
     </row>
@@ -2511,7 +2511,7 @@
         <v>8320</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>482.56</v>
+        <v>515.84</v>
       </c>
       <c r="I40" s="2" t="n">
         <v>9792000</v>
@@ -2523,7 +2523,7 @@
         <v>12729600</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>738317</v>
+        <v>789235</v>
       </c>
       <c r="M40" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>5330</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>309.14</v>
+        <v>330.46</v>
       </c>
       <c r="I41" s="2" t="n">
         <v>5510400</v>
@@ -2568,7 +2568,7 @@
         <v>7163520</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>415484</v>
+        <v>444138</v>
       </c>
       <c r="M41" t="inlineStr"/>
     </row>
@@ -2601,7 +2601,7 @@
         <v>5980</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>346.84</v>
+        <v>370.76</v>
       </c>
       <c r="I42" s="2" t="n">
         <v>5740800</v>
@@ -2613,7 +2613,7 @@
         <v>7463040</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>432856</v>
+        <v>462708</v>
       </c>
       <c r="M42" t="inlineStr"/>
     </row>
@@ -2646,7 +2646,7 @@
         <v>3575</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>207.35</v>
+        <v>221.65</v>
       </c>
       <c r="I43" s="2" t="n">
         <v>2805000</v>
@@ -2658,7 +2658,7 @@
         <v>3646500</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>211497</v>
+        <v>226083</v>
       </c>
       <c r="M43" t="inlineStr"/>
     </row>
@@ -2691,7 +2691,7 @@
         <v>7410</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>429.78</v>
+        <v>459.42</v>
       </c>
       <c r="I44" s="2" t="n">
         <v>6002100</v>
@@ -2703,7 +2703,7 @@
         <v>7802730</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>452558</v>
+        <v>483769</v>
       </c>
       <c r="M44" t="inlineStr"/>
     </row>
@@ -2736,7 +2736,7 @@
         <v>6175</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>358.15</v>
+        <v>382.85</v>
       </c>
       <c r="I45" s="2" t="n">
         <v>2280000</v>
@@ -2748,7 +2748,7 @@
         <v>2964000</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>171912</v>
+        <v>183768</v>
       </c>
       <c r="M45" t="inlineStr"/>
     </row>
@@ -2781,7 +2781,7 @@
         <v>9750</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>565.5</v>
+        <v>604.5</v>
       </c>
       <c r="I46" s="2" t="n">
         <v>3150000</v>
@@ -2793,7 +2793,7 @@
         <v>4095000</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>237510</v>
+        <v>253890</v>
       </c>
       <c r="M46" t="inlineStr"/>
     </row>
@@ -2826,7 +2826,7 @@
         <v>7605</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>441.09</v>
+        <v>471.51</v>
       </c>
       <c r="I47" s="2" t="n">
         <v>3510000</v>
@@ -2838,7 +2838,7 @@
         <v>4563000</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>264654</v>
+        <v>282906</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -2979,10 +2979,10 @@
         <v>10300</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>11380</v>
+        <v>11310</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>660.02</v>
+        <v>701.22</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>154500000</v>
@@ -2994,10 +2994,10 @@
         <v>903972</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>170694551</v>
+        <v>169649741</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>9900284</v>
+        <v>10518284</v>
       </c>
     </row>
     <row r="3">
@@ -3031,10 +3031,10 @@
         <v>4000</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>4419</v>
+        <v>4392</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>256.32</v>
+        <v>272.32</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>4000000</v>
@@ -3046,10 +3046,10 @@
         <v>35566</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4419276</v>
+        <v>4392226</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>256318</v>
+        <v>272318</v>
       </c>
     </row>
     <row r="4">
@@ -3083,10 +3083,10 @@
         <v>4130</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>4563</v>
+        <v>4535</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>264.65</v>
+        <v>281.17</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>826000</v>
@@ -3098,10 +3098,10 @@
         <v>7113</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>912581</v>
+        <v>906995</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>52930</v>
+        <v>56234</v>
       </c>
     </row>
     <row r="5">
@@ -3135,10 +3135,10 @@
         <v>4130</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>4563</v>
+        <v>4535</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>264.65</v>
+        <v>281.17</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1652000</v>
@@ -3150,10 +3150,10 @@
         <v>14226</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1825161</v>
+        <v>1813989</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>105859</v>
+        <v>112467</v>
       </c>
     </row>
     <row r="6">
@@ -3187,10 +3187,10 @@
         <v>3190</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>3524</v>
+        <v>3503</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>204.41</v>
+        <v>217.17</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>2233000</v>
@@ -3202,10 +3202,10 @@
         <v>24896</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2467061</v>
+        <v>2451960</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>143090</v>
+        <v>152022</v>
       </c>
     </row>
     <row r="7">
@@ -3239,10 +3239,10 @@
         <v>3190</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>3524</v>
+        <v>3503</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>204.41</v>
+        <v>217.17</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1276000</v>
@@ -3254,10 +3254,10 @@
         <v>14226</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1409749</v>
+        <v>1401120</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>81765</v>
+        <v>86869</v>
       </c>
     </row>
   </sheetData>
@@ -3333,7 +3333,7 @@
         <v>392742454</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>22779063</v>
+        <v>24350033</v>
       </c>
     </row>
     <row r="3">
@@ -3355,7 +3355,7 @@
         <v>238772820</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>13848823</v>
+        <v>14803916</v>
       </c>
     </row>
     <row r="4">
@@ -3377,7 +3377,7 @@
         <v>45864390</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2660134</v>
+        <v>2843591</v>
       </c>
     </row>
     <row r="5">
@@ -3399,7 +3399,7 @@
         <v>40281800</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2336344</v>
+        <v>2497472</v>
       </c>
     </row>
     <row r="6">
@@ -3421,7 +3421,7 @@
         <v>26453960</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1534330</v>
+        <v>1640146</v>
       </c>
     </row>
     <row r="7">
@@ -3443,7 +3443,7 @@
         <v>5697120</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>330433</v>
+        <v>353221</v>
       </c>
     </row>
     <row r="8">
@@ -3465,7 +3465,7 @@
         <v>4563000</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>264654</v>
+        <v>282906</v>
       </c>
     </row>
   </sheetData>
